--- a/output/pdf_financials_xlsx/TBL.xlsx
+++ b/output/pdf_financials_xlsx/TBL.xlsx
@@ -54640,7 +54640,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -55635,7 +55635,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E534" s="5" t="n">

--- a/output/pdf_financials_xlsx/TBL.xlsx
+++ b/output/pdf_financials_xlsx/TBL.xlsx
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.922</v>
+        <v>17.091</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.883</v>
+        <v>33.827</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.258</v>
+        <v>22.87</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>7.237</v>
@@ -2394,10 +2394,8 @@
       <c r="F37" s="3" t="n">
         <v>136.102</v>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="3" t="n">
+        <v>116.615</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>118.934</v>
@@ -2545,48 +2543,46 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>5.268</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>3.459</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>2.323</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.979</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3.425</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>3.312</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>1.871</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>1.662</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.599</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>2.473</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>4.988</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>14.364</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>6.062</v>
       </c>
     </row>
     <row r="41">
@@ -2599,16 +2595,16 @@
         <v>134.397</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>125.823</v>
+        <v>131.091</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>104.974</v>
+        <v>108.433</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>126.878</v>
+        <v>129.201</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>136.102</v>
+        <v>141.081</v>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
@@ -2616,31 +2612,31 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>118.934</v>
+        <v>122.246</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>135.746</v>
+        <v>137.617</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>139.25</v>
+        <v>140.912</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>94.514</v>
+        <v>98.113</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>85.334</v>
+        <v>87.807</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>123.098</v>
+        <v>132.958</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>119.429</v>
+        <v>124.417</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>119.429</v>
+        <v>133.793</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>150.387</v>
+        <v>156.449</v>
       </c>
     </row>
     <row r="42">
@@ -2983,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.351</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.302</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2994,31 +2990,31 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.229</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.317</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.816</v>
+        <v>0.154</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.924</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.814</v>
+        <v>0.341</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.011</v>
+        <v>10.151</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>19.682</v>
+        <v>14.694</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>19.682</v>
+        <v>5.318</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>8.645</v>
+        <v>2.583</v>
       </c>
     </row>
     <row r="49">
@@ -4275,22 +4271,22 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>2.493</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>5.408</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>5.527</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>5.527</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>6.015</v>
       </c>
     </row>
     <row r="71">
@@ -4329,22 +4325,22 @@
         <v>101.625</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>72.274</v>
+        <v>74.767</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>48.321</v>
+        <v>52.752</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>5.408</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>5.527</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>5.527</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>6.015</v>
       </c>
     </row>
     <row r="72">
@@ -4843,30 +4839,22 @@
         <v>5.147750639450323</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.7890808581137051</v>
+        <v>0.8101533311919936</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.4212723003350419</v>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.4529939005183128</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.01488790027749637</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01397761356336838</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.01363284313967313</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.01295230794408221</v>
       </c>
     </row>
     <row r="81">
@@ -6563,49 +6551,49 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="113">
@@ -7058,19 +7046,19 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-1.658</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-4.154</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.094</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.601</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
@@ -9380,7 +9368,11 @@
           <t>Current portion of lease obligations (Note 13) 6,544</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11338,7 +11330,11 @@
           <t>Current portion of lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12845,7 +12841,11 @@
           <t>Current portion of lease obligations (Note 15)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -31541,7 +31541,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>0.134</v>
       </c>
@@ -31930,7 +31934,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -35405,7 +35413,11 @@
           <t>Proceeds from disposition of property, plant and equipment 671</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -40059,7 +40071,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E358" s="5" t="n">
         <v>-3.994</v>
       </c>
@@ -54551,7 +54567,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E522" s="5" t="n">
         <v>17.091</v>
       </c>
